--- a/data/trans_dic/P6905-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P6905-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores de cabeza</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores de cabeza (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,78; 43,63</t>
+          <t>16,52; 43,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 45,26</t>
+          <t>5,66; 47,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,83; 76,62</t>
+          <t>34,09; 77,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,68; 61,82</t>
+          <t>9,71; 69,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,27; 66,88</t>
+          <t>14,84; 73,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,44; 74,42</t>
+          <t>10,57; 74,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,72; 49,75</t>
+          <t>26,0; 49,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 36,63</t>
+          <t>4,71; 38,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,53; 45,93</t>
+          <t>13,73; 47,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,89; 61,05</t>
+          <t>7,69; 59,29</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,93; 43,57</t>
+          <t>26,27; 43,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,57; 42,62</t>
+          <t>22,04; 43,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,01; 35,99</t>
+          <t>16,32; 36,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,19; 61,28</t>
+          <t>25,22; 59,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,78; 56,46</t>
+          <t>34,73; 55,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,57; 50,09</t>
+          <t>25,32; 51,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,13; 60,57</t>
+          <t>32,31; 59,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,33; 62,53</t>
+          <t>30,72; 59,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,78; 45,13</t>
+          <t>31,72; 45,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,82; 42,59</t>
+          <t>26,37; 42,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24,79; 41,16</t>
+          <t>25,23; 41,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,89; 56,15</t>
+          <t>32,66; 56,02</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,35; 36,76</t>
+          <t>19,42; 35,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,01; 36,46</t>
+          <t>18,55; 36,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,38; 38,36</t>
+          <t>20,03; 37,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,37; 29,13</t>
+          <t>12,19; 29,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,68; 47,91</t>
+          <t>25,82; 48,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,23; 62,0</t>
+          <t>36,64; 61,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,04; 48,45</t>
+          <t>25,3; 47,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,64; 39,29</t>
+          <t>21,78; 39,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,52; 37,15</t>
+          <t>23,81; 36,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,21; 43,62</t>
+          <t>29,65; 44,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25,38; 39,78</t>
+          <t>25,2; 38,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,9; 31,03</t>
+          <t>18,73; 31,87</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,21; 38,62</t>
+          <t>20,82; 39,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,33; 36,62</t>
+          <t>16,11; 35,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,6; 39,59</t>
+          <t>21,17; 40,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,74; 27,25</t>
+          <t>11,78; 27,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,63; 50,29</t>
+          <t>19,22; 50,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,11; 53,3</t>
+          <t>20,17; 51,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,53; 54,02</t>
+          <t>27,4; 52,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,36; 40,62</t>
+          <t>14,07; 40,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,95; 38,43</t>
+          <t>22,2; 38,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,44; 36,71</t>
+          <t>19,96; 36,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,31; 41,61</t>
+          <t>25,3; 42,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,69; 32,62</t>
+          <t>15,99; 31,41</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,47; 42,33</t>
+          <t>16,1; 42,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,74; 36,33</t>
+          <t>10,02; 38,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,04; 42,29</t>
+          <t>14,6; 41,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,85; 31,78</t>
+          <t>12,74; 30,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,17; 64,12</t>
+          <t>14,19; 64,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,85; 62,43</t>
+          <t>18,79; 60,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,01; 73,18</t>
+          <t>33,72; 70,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,02; 37,41</t>
+          <t>20,37; 38,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,11; 42,27</t>
+          <t>19,47; 44,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,96; 40,19</t>
+          <t>17,9; 41,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26,11; 50,08</t>
+          <t>25,85; 51,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,58; 30,43</t>
+          <t>17,6; 30,41</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,16</t>
+          <t>0,0; 81,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,84</t>
+          <t>0,0; 53,06</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>25,47; 34,65</t>
+          <t>26,21; 35,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,41; 31,37</t>
+          <t>21,42; 30,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,91; 32,71</t>
+          <t>22,48; 32,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,89; 29,25</t>
+          <t>18,32; 28,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>35,05; 47,36</t>
+          <t>34,53; 47,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,47; 48,33</t>
+          <t>33,72; 48,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,99; 48,37</t>
+          <t>34,46; 48,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>23,67; 38,34</t>
+          <t>23,43; 38,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,19; 37,43</t>
+          <t>29,6; 37,08</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27,81; 36,27</t>
+          <t>28,28; 35,76</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28,26; 36,42</t>
+          <t>28,62; 36,76</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,13; 31,49</t>
+          <t>23,19; 31,74</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores de cabeza</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores de cabeza (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7284; 20143</t>
+          <t>7627; 20267</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1764</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>998; 7763</t>
+          <t>971; 8103</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2171</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6719; 15215</t>
+          <t>6770; 15378</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>973; 6216</t>
+          <t>976; 6982</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1778; 7787</t>
+          <t>1728; 8559</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1601; 11419</t>
+          <t>1622; 11477</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16983; 32851</t>
+          <t>17168; 32766</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>977; 7466</t>
+          <t>959; 7944</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3897; 13225</t>
+          <t>3955; 13659</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1897; 13025</t>
+          <t>1642; 12648</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38325; 61990</t>
+          <t>37386; 61420</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18610; 36778</t>
+          <t>19021; 37565</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13872; 29357</t>
+          <t>13312; 30010</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14879; 36201</t>
+          <t>14898; 35403</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26777; 44760</t>
+          <t>27534; 44247</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17160; 33617</t>
+          <t>16994; 34296</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14871; 28040</t>
+          <t>14957; 27729</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16150; 31232</t>
+          <t>15345; 29963</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70413; 99984</t>
+          <t>70285; 99957</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41139; 65334</t>
+          <t>40454; 64729</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31703; 52622</t>
+          <t>32264; 53650</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34765; 61216</t>
+          <t>35603; 61069</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24392; 46324</t>
+          <t>24470; 44309</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18604; 35686</t>
+          <t>18157; 35490</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23056; 43392</t>
+          <t>22657; 42815</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11818; 27832</t>
+          <t>11643; 27919</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17985; 33560</t>
+          <t>18082; 34050</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27044; 45029</t>
+          <t>26612; 44520</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18610; 34623</t>
+          <t>18081; 34187</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16352; 29685</t>
+          <t>16456; 30189</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46110; 72847</t>
+          <t>46690; 71363</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49802; 74382</t>
+          <t>50553; 75928</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46854; 73435</t>
+          <t>46520; 71878</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32342; 53093</t>
+          <t>32040; 54524</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22451; 42909</t>
+          <t>23132; 44014</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14705; 32973</t>
+          <t>14504; 31747</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18834; 36195</t>
+          <t>19358; 37450</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12749; 29577</t>
+          <t>12785; 30097</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7271; 18627</t>
+          <t>7119; 18603</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8336; 22092</t>
+          <t>8360; 21523</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14323; 30311</t>
+          <t>15375; 29682</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22247; 62937</t>
+          <t>21801; 62471</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34003; 56935</t>
+          <t>32890; 57207</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26880; 48270</t>
+          <t>26252; 48429</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37339; 61394</t>
+          <t>37326; 62200</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43974; 85956</t>
+          <t>42135; 82771</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7098; 19423</t>
+          <t>7387; 19296</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4792; 14824</t>
+          <t>4088; 15625</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6296; 18966</t>
+          <t>6549; 18479</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7993; 21433</t>
+          <t>8588; 20724</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1971; 8918</t>
+          <t>1974; 9000</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4918; 14727</t>
+          <t>4433; 14319</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9859; 22540</t>
+          <t>10386; 21812</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11110; 20763</t>
+          <t>11305; 21355</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11423; 25271</t>
+          <t>11641; 26367</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11565; 25883</t>
+          <t>11526; 26696</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19754; 37881</t>
+          <t>19554; 38852</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21610; 37417</t>
+          <t>21632; 37386</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1070</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 894</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2365</t>
+          <t>0; 2370</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 1070</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 3259</t>
+          <t>0; 3097</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>188; 821</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>188; 821</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>120280; 163652</t>
+          <t>123771; 166150</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>69651; 102071</t>
+          <t>69688; 100601</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>80193; 114490</t>
+          <t>78681; 112585</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>60738; 99292</t>
+          <t>62196; 97889</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>77154; 104241</t>
+          <t>76002; 104901</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>74043; 103828</t>
+          <t>72440; 103677</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>75682; 104613</t>
+          <t>74529; 104549</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>83849; 135810</t>
+          <t>82978; 136476</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>209046; 259159</t>
+          <t>204964; 256786</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>150211; 195919</t>
+          <t>152744; 193169</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>160012; 206249</t>
+          <t>162076; 208156</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>160456; 218460</t>
+          <t>160841; 220170</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6905-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P6905-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,52; 43,89</t>
+          <t>16,23; 42,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,66; 47,25</t>
+          <t>5,74; 45,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,09; 77,44</t>
+          <t>34,48; 79,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,71; 69,43</t>
+          <t>0,0; 60,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,84; 73,51</t>
+          <t>15,58; 71,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,57; 74,8</t>
+          <t>11,48; 77,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,0; 49,62</t>
+          <t>26,22; 48,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 38,98</t>
+          <t>4,8; 34,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,73; 47,44</t>
+          <t>13,25; 45,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,69; 59,29</t>
+          <t>6,6; 55,83</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>45,27%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,27; 43,16</t>
+          <t>26,88; 43,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,04; 43,53</t>
+          <t>21,82; 43,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,32; 36,79</t>
+          <t>15,68; 36,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,22; 59,93</t>
+          <t>30,52; 64,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,73; 55,81</t>
+          <t>33,31; 55,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,32; 51,1</t>
+          <t>25,33; 50,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,31; 59,9</t>
+          <t>31,74; 60,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,72; 59,99</t>
+          <t>29,73; 59,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,72; 45,11</t>
+          <t>31,44; 44,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,37; 42,2</t>
+          <t>27,42; 43,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,23; 41,96</t>
+          <t>25,37; 41,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,66; 56,02</t>
+          <t>34,15; 56,4</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,42; 35,16</t>
+          <t>19,09; 35,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,55; 36,26</t>
+          <t>18,8; 36,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,03; 37,85</t>
+          <t>20,16; 39,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,19; 29,23</t>
+          <t>13,34; 30,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,82; 48,61</t>
+          <t>25,52; 48,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,64; 61,3</t>
+          <t>36,42; 61,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,3; 47,84</t>
+          <t>25,8; 49,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,78; 39,96</t>
+          <t>20,89; 37,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,81; 36,4</t>
+          <t>23,29; 37,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,65; 44,53</t>
+          <t>30,03; 44,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25,2; 38,94</t>
+          <t>25,21; 38,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,73; 31,87</t>
+          <t>19,31; 31,99</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,82; 39,61</t>
+          <t>20,63; 39,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,11; 35,25</t>
+          <t>15,9; 35,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,17; 40,96</t>
+          <t>20,41; 39,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,78; 27,73</t>
+          <t>14,03; 30,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,22; 50,23</t>
+          <t>18,9; 50,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,17; 51,93</t>
+          <t>20,66; 51,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,4; 52,9</t>
+          <t>26,2; 52,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,07; 40,32</t>
+          <t>26,82; 40,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,2; 38,62</t>
+          <t>22,65; 39,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,96; 36,83</t>
+          <t>19,73; 36,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,3; 42,16</t>
+          <t>25,2; 41,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,99; 31,41</t>
+          <t>22,68; 33,28</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,1; 42,06</t>
+          <t>15,41; 41,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,02; 38,29</t>
+          <t>9,9; 36,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,6; 41,2</t>
+          <t>14,11; 42,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,74; 30,73</t>
+          <t>12,97; 32,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,19; 64,7</t>
+          <t>14,34; 64,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,79; 60,7</t>
+          <t>21,69; 62,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,72; 70,82</t>
+          <t>32,56; 72,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,37; 38,47</t>
+          <t>20,12; 38,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,47; 44,1</t>
+          <t>18,07; 41,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,9; 41,46</t>
+          <t>18,85; 40,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,85; 51,36</t>
+          <t>25,44; 49,38</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,6; 30,41</t>
+          <t>18,76; 31,12</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,35</t>
+          <t>0,0; 86,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,06</t>
+          <t>0,0; 51,74</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>26,21; 35,18</t>
+          <t>25,66; 34,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,42; 30,92</t>
+          <t>21,08; 31,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,48; 32,17</t>
+          <t>22,77; 32,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18,32; 28,83</t>
+          <t>20,28; 30,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,53; 47,66</t>
+          <t>34,12; 48,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,72; 48,26</t>
+          <t>33,92; 47,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,46; 48,34</t>
+          <t>34,96; 48,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>23,43; 38,53</t>
+          <t>28,95; 38,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29,6; 37,08</t>
+          <t>29,8; 37,02</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28,28; 35,76</t>
+          <t>28,2; 36,87</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28,62; 36,76</t>
+          <t>28,67; 36,51</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,19; 31,74</t>
+          <t>26,02; 32,97</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>6870</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7627; 20267</t>
+          <t>7493; 19635</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>971; 8103</t>
+          <t>984; 7869</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2088,42 +2088,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6770; 15378</t>
+          <t>6847; 15815</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>976; 6982</t>
+          <t>0; 6108</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1728; 8559</t>
+          <t>1814; 8267</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1622; 11477</t>
+          <t>1825; 12376</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17168; 32766</t>
+          <t>17316; 32284</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>959; 7944</t>
+          <t>979; 7095</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3955; 13659</t>
+          <t>3816; 13031</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1642; 12648</t>
+          <t>1658; 14022</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24664</t>
+          <t>32277</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22764</t>
+          <t>22551</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>47428</t>
+          <t>54829</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37386; 61420</t>
+          <t>38241; 61899</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19021; 37565</t>
+          <t>18824; 37206</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13312; 30010</t>
+          <t>12792; 29998</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14898; 35403</t>
+          <t>21238; 44554</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27534; 44247</t>
+          <t>26406; 43883</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16994; 34296</t>
+          <t>17000; 33930</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14957; 27729</t>
+          <t>14691; 27853</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15345; 29963</t>
+          <t>15316; 30430</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70285; 99957</t>
+          <t>69658; 99214</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40454; 64729</t>
+          <t>42065; 66720</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32264; 53650</t>
+          <t>32436; 52984</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35603; 61069</t>
+          <t>41360; 68307</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>23485</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22768</t>
+          <t>24750</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41944</t>
+          <t>48234</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24470; 44309</t>
+          <t>24053; 44231</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18157; 35490</t>
+          <t>18401; 35954</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22657; 42815</t>
+          <t>22807; 44480</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11643; 27919</t>
+          <t>14672; 33963</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18082; 34050</t>
+          <t>17876; 33652</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26612; 44520</t>
+          <t>26455; 44386</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18081; 34187</t>
+          <t>18437; 35138</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16456; 30189</t>
+          <t>18102; 32180</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46690; 71363</t>
+          <t>45663; 72673</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50553; 75928</t>
+          <t>51209; 75599</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46520; 71878</t>
+          <t>46525; 71020</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32040; 54524</t>
+          <t>37973; 62904</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20219</t>
+          <t>25566</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>45763</t>
+          <t>43182</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65981</t>
+          <t>68748</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23132; 44014</t>
+          <t>22920; 43904</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14504; 31747</t>
+          <t>14316; 31904</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19358; 37450</t>
+          <t>18660; 36072</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12785; 30097</t>
+          <t>16910; 36925</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7119; 18603</t>
+          <t>6999; 18563</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8360; 21523</t>
+          <t>8563; 21432</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15375; 29682</t>
+          <t>14700; 29561</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21801; 62471</t>
+          <t>33926; 51799</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32890; 57207</t>
+          <t>33558; 58328</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26252; 48429</t>
+          <t>25945; 48193</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37326; 62200</t>
+          <t>37172; 60576</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42135; 82771</t>
+          <t>56031; 82208</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13491</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15793</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29283</t>
+          <t>33368</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7387; 19296</t>
+          <t>7070; 19170</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4088; 15625</t>
+          <t>4040; 14878</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6549; 18479</t>
+          <t>6328; 19003</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8588; 20724</t>
+          <t>9344; 23745</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1974; 9000</t>
+          <t>1994; 9038</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4433; 14319</t>
+          <t>5116; 14760</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10386; 21812</t>
+          <t>10028; 22185</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11305; 21355</t>
+          <t>12429; 23611</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11641; 26367</t>
+          <t>10806; 24977</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11526; 26696</t>
+          <t>12141; 25836</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19554; 38852</t>
+          <t>19241; 37355</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21632; 37386</t>
+          <t>25102; 41633</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1049</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2370</t>
+          <t>0; 2603</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 3097</t>
+          <t>0; 3449</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>77549</t>
+          <t>97134</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>114409</t>
+          <t>115965</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>191958</t>
+          <t>213098</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>123771; 166150</t>
+          <t>121184; 162733</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>69688; 100601</t>
+          <t>68592; 101076</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>78681; 112585</t>
+          <t>79689; 114016</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>62196; 97889</t>
+          <t>78078; 117943</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>76002; 104901</t>
+          <t>75100; 105759</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>72440; 103677</t>
+          <t>72880; 103075</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>74529; 104549</t>
+          <t>75610; 105648</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>82978; 136476</t>
+          <t>99979; 134155</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>204964; 256786</t>
+          <t>206311; 256365</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>152744; 193169</t>
+          <t>152324; 199139</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>162076; 208156</t>
+          <t>162334; 206760</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>160841; 220170</t>
+          <t>190026; 240821</t>
         </is>
       </c>
     </row>
